--- a/projects/01_STM32_DAQ_Control_Board/hardware/outputs/bom/STM32_DAQ_Control_Board.xlsx
+++ b/projects/01_STM32_DAQ_Control_Board/hardware/outputs/bom/STM32_DAQ_Control_Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hardware-Practice-Projects\projects\01_STM32_DAQ_Control_Board\hardware\outputs\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68A864DA-2503-4965-8DE8-81F1FE63E50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C58161B0-35E1-41AE-81FF-79D9BFAA6117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36390" yWindow="2355" windowWidth="19200" windowHeight="11085" xr2:uid="{3AA1C4B7-C342-429E-8325-F92140B52A68}"/>
+    <workbookView xWindow="36390" yWindow="2355" windowWidth="19200" windowHeight="11085" xr2:uid="{92212D09-E668-4A2D-A10E-1175C0F6AE1F}"/>
   </bookViews>
   <sheets>
     <sheet name="STM32_DAQ_Control_Board" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="136">
-  <si>
-    <t>Comment</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="122">
+  <si>
+    <t>Line #</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
   <si>
     <t>Description</t>
@@ -53,34 +56,43 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>Footprint</t>
-  </si>
-  <si>
-    <t>LibRef</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
+    <t>Manufacturer 1</t>
+  </si>
+  <si>
+    <t>Manufacturer Part Number 1</t>
+  </si>
+  <si>
+    <t>Manufacturer Lifecycle 1</t>
+  </si>
+  <si>
+    <t>Supplier 1</t>
+  </si>
+  <si>
+    <t>Supplier Part Number 1</t>
+  </si>
+  <si>
+    <t>Supplier Unit Price 1</t>
+  </si>
+  <si>
+    <t>Supplier Subtotal 1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>4.7uf</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>C1, C17</t>
   </si>
   <si>
-    <t>C0603</t>
-  </si>
-  <si>
-    <t>CAP_0603</t>
-  </si>
-  <si>
     <t>100nF</t>
   </si>
   <si>
-    <t>C2, C5, C6, C7, C9, C12, C14</t>
+    <t>C2, C5, C6, C9, C12, C14</t>
   </si>
   <si>
     <t>5.1pF</t>
@@ -89,6 +101,12 @@
     <t>C3, C4</t>
   </si>
   <si>
+    <t>100nf</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
     <t>1uf</t>
   </si>
   <si>
@@ -101,6 +119,15 @@
     <t>C10, C11</t>
   </si>
   <si>
+    <t>1nF</t>
+  </si>
+  <si>
+    <t>容值:1nF;精度:±10%;额定电压:1kV;温度系数:X7R;</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
     <t>SS14</t>
   </si>
   <si>
@@ -110,12 +137,6 @@
     <t>D1, D2</t>
   </si>
   <si>
-    <t>SMA_L4.3-W2.6-LS5.2-RD</t>
-  </si>
-  <si>
-    <t>SS14_C83852</t>
-  </si>
-  <si>
     <t>BAT54S</t>
   </si>
   <si>
@@ -125,12 +146,6 @@
     <t>D3, D4</t>
   </si>
   <si>
-    <t>SOT-23-3_L2.9-W1.3-P1.90-LS2.4-BR</t>
-  </si>
-  <si>
-    <t>BAT54S_C7420333</t>
-  </si>
-  <si>
     <t>SMF5.0A</t>
   </si>
   <si>
@@ -140,12 +155,6 @@
     <t>D5</t>
   </si>
   <si>
-    <t>SOD-123FL_L2.7-W1.8-LS3.8-RD</t>
-  </si>
-  <si>
-    <t>SMF5.0A_C19077497</t>
-  </si>
-  <si>
     <t>SMD0805-050-6</t>
   </si>
   <si>
@@ -155,19 +164,13 @@
     <t>F1</t>
   </si>
   <si>
-    <t>F0805</t>
-  </si>
-  <si>
     <t>2.54-1*3P针</t>
   </si>
   <si>
     <t>插针结构:1x3P;间距:2.54mm;行距:-;圆针/方针:方针;安装方式:直插;排数:单排;总PIN位数:3P;额定电流:3A;额定电压:-;配合针长度:6mm;塑高:2.5mm;端接针长度:3mm;触头材质:黄铜;触头镀层:金;工作温度:-40℃~+105℃;颜色:黑色;</t>
   </si>
   <si>
-    <t>H1, H3, H6</t>
-  </si>
-  <si>
-    <t>HDR-TH_3P-P2.54-V-M-1</t>
+    <t>H1, H3</t>
   </si>
   <si>
     <t>HX PZ2.54-1x3P ZZ</t>
@@ -179,9 +182,6 @@
     <t>H2</t>
   </si>
   <si>
-    <t>CONN-TH_HX-PZ2.54-1X3P-ZZ</t>
-  </si>
-  <si>
     <t>PH2.54-1X5P-H25</t>
   </si>
   <si>
@@ -191,9 +191,6 @@
     <t>H4</t>
   </si>
   <si>
-    <t>HDR-TH_5P-P2.54-V-M-3</t>
-  </si>
-  <si>
     <t>PZ2.54-2X5P-H25</t>
   </si>
   <si>
@@ -203,7 +200,7 @@
     <t>H5</t>
   </si>
   <si>
-    <t>HDR-TH_10P-P2.54-V-M-R2-C5-S2.54_2</t>
+    <t>H6</t>
   </si>
   <si>
     <t>GL0603UR01</t>
@@ -212,10 +209,10 @@
     <t>灯头类型:-;发光颜色:红色;正向压降(Vf):2.4V;功率:-;正向电流:20mA;波长:620nm~625nm;二极管配置:独立二极管;透镜颜色:无色透明透镜;色温:-;发光强度:120mcd;发光角度:120°;载带方式:正贴;工作温度:-40℃~+85℃;</t>
   </si>
   <si>
-    <t>LED1, LED2</t>
-  </si>
-  <si>
-    <t>LED0603-FD</t>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>LED2</t>
   </si>
   <si>
     <t>AO3400A</t>
@@ -227,25 +224,16 @@
     <t>Q1, Q2</t>
   </si>
   <si>
-    <t>AO3400A_C20917</t>
-  </si>
-  <si>
     <t>100欧</t>
   </si>
   <si>
     <t>R1, R6</t>
   </si>
   <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>Res_0603</t>
-  </si>
-  <si>
     <t>10K</t>
   </si>
   <si>
-    <t>R2, R17, R21</t>
+    <t>R2, R17</t>
   </si>
   <si>
     <t>100k</t>
@@ -257,16 +245,13 @@
     <t>1k</t>
   </si>
   <si>
-    <t>R4, R18</t>
-  </si>
-  <si>
-    <t>Res_0603_1, Res_0603</t>
+    <t>R4</t>
   </si>
   <si>
     <t>0欧</t>
   </si>
   <si>
-    <t>R5, R15</t>
+    <t>R5</t>
   </si>
   <si>
     <t>12K</t>
@@ -293,22 +278,40 @@
     <t>R14, R16</t>
   </si>
   <si>
+    <t>1MΩ</t>
+  </si>
+  <si>
+    <t>电阻类型:厚膜电阻;阻值:1MΩ;精度:±1%;功率:125mW;工作电压:150V;温度系数:±100ppm/℃;</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
     <t>4.7k</t>
   </si>
   <si>
     <t>R19, R20</t>
   </si>
   <si>
+    <t>R21</t>
+  </si>
+  <si>
     <t>TS-1088-AR02016</t>
   </si>
   <si>
     <t>电路结构:单刀单掷;按钮形状:圆形按钮;作用力:1.6N;安装方式:立贴;开关长度:3.9mm;开关宽度:3mm;开关高度:2mm;带支架:不带支架;触点电流:50mA;额定电压:12V;带灯:-;工作寿命:10万次;</t>
   </si>
   <si>
-    <t>SW1, SW2</t>
-  </si>
-  <si>
-    <t>SW-SMD_L3.9-W3.0-P4.45</t>
+    <t>SW1</t>
+  </si>
+  <si>
+    <t>SW2</t>
   </si>
   <si>
     <t>RS601HL-1010011BB</t>
@@ -320,21 +323,12 @@
     <t>SW3</t>
   </si>
   <si>
-    <t>SW-TH_RS601HL-1010011BB</t>
-  </si>
-  <si>
     <t>Test Point 测试点</t>
   </si>
   <si>
     <t>TP_1, TP_2, TP_ADC1, TP_ADC2, TP_GATE1, TP_GATE2, TP_GND1, TP_OUT1, TP_OUT2, TP_VBUS1</t>
   </si>
   <si>
-    <t>Test-Point-0.5mm</t>
-  </si>
-  <si>
-    <t>Test-Point</t>
-  </si>
-  <si>
     <t>STM32F103C8T6</t>
   </si>
   <si>
@@ -344,9 +338,6 @@
     <t>U1</t>
   </si>
   <si>
-    <t>LQFP-48_L7.0-W7.0-P0.50-LS9.0-BL</t>
-  </si>
-  <si>
     <t>HX PZ2.54-1x2P ZZ</t>
   </si>
   <si>
@@ -356,9 +347,6 @@
     <t>U2, U3</t>
   </si>
   <si>
-    <t>HDR-TH_2P-P2.54-V-M-3</t>
-  </si>
-  <si>
     <t>HX PZ2.54-1x5P</t>
   </si>
   <si>
@@ -368,12 +356,6 @@
     <t>U4</t>
   </si>
   <si>
-    <t>HDR-TH_5P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>HX PZ2.54-1x5P ZZ</t>
-  </si>
-  <si>
     <t>HX PZ2.54-1x4P</t>
   </si>
   <si>
@@ -383,12 +365,6 @@
     <t>U5</t>
   </si>
   <si>
-    <t>HDR-TH_4P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>HX PZ2.54-1x4P ZZ</t>
-  </si>
-  <si>
     <t>TPD2EUSB30DRTR-N</t>
   </si>
   <si>
@@ -398,9 +374,6 @@
     <t>U6</t>
   </si>
   <si>
-    <t>SOT-723_L1.2-W0.8-P0.40-LS1.2-BR</t>
-  </si>
-  <si>
     <t>CH340C</t>
   </si>
   <si>
@@ -410,9 +383,6 @@
     <t>U7</t>
   </si>
   <si>
-    <t>SOP-16_L10.0-W3.9-P1.27-LS6.0-BL</t>
-  </si>
-  <si>
     <t>AP2112K-3.3TRG1</t>
   </si>
   <si>
@@ -422,19 +392,13 @@
     <t>U8</t>
   </si>
   <si>
-    <t>SOT-25-5_L2.9-W1.6-P0.95-LS2.8-BL</t>
-  </si>
-  <si>
-    <t>TYPE-C 16PIN 2MD(073)</t>
-  </si>
-  <si>
-    <t>连接器类型:Type-C;协议标准:-;公母:母;安装方式:卧贴;触点数量:16P;端口数量:1;额定电流 - 电源:3A;工作温度:-25℃~+85℃;</t>
-  </si>
-  <si>
-    <t>USB1</t>
-  </si>
-  <si>
-    <t>USB-C-SMD_TYPE-C-16PIN-2MD-073</t>
+    <t>TYPE-C-31-M-12</t>
+  </si>
+  <si>
+    <t>连接器类型:Type-C;协议标准:-;公母:母;安装方式:卧贴;触点数量:16P;端口数量:1;额定电流 - 电源:5A;工作温度:-30℃~+80℃;</t>
+  </si>
+  <si>
+    <t>USBC1</t>
   </si>
   <si>
     <t>8MHz</t>
@@ -444,12 +408,6 @@
   </si>
   <si>
     <t>X1</t>
-  </si>
-  <si>
-    <t>CRYSTAL-SMD_L5.0-W3.2</t>
-  </si>
-  <si>
-    <t>XC53G2-8.000-F12NJHP</t>
   </si>
 </sst>
 </file>
@@ -865,14 +823,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F269CA81-74DE-4A9F-AA60-D66E46AE05A2}">
-  <dimension ref="A1:F38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A6B1510-1CC7-4EBB-B5E7-4D1119B3CA84}">
+  <dimension ref="A1:L46"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="8.1640625" customWidth="1"/>
+    <col min="2" max="4" width="14.58203125" customWidth="1"/>
+    <col min="5" max="5" width="9.9140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="10.9140625" customWidth="1"/>
+    <col min="10" max="10" width="20.4140625" customWidth="1"/>
+    <col min="11" max="11" width="18.1640625" customWidth="1"/>
+    <col min="12" max="12" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -891,131 +858,171 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1025,612 +1032,908 @@
       <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="1">
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="E13" s="1">
+        <v>2</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="C20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="C21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="1">
+      <c r="E21" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="C23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="1">
+      <c r="E23" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="C25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="1">
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F20" s="1">
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" s="1">
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" s="1">
+      <c r="C29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="B30" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F23" s="1">
+      <c r="C30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="1">
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" s="1">
+        <v>10</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E39" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F29" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F31" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F36" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F37" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F38" s="1">
-        <v>1</v>
-      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
